--- a/data_extactor/batch_10_fa/batch_0096_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0096_fa.xlsx
@@ -508,27 +508,27 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>سخن‌گفتن | گوش‌دادن فعال | مانیتورینگ | درک مطلب | تفکر انتقادی | یادگیری فعال | نگارش</t>
+          <t>سخن گفتن | گوش دادن فعال | نظارت | درک مطلب | تفکر انتقادی | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | ایمنی و امنیت عمومی | زبان انگلیسی | حمل‌ونقل | روان‌شناسی | جغرافیا | کامپیوتر و الکترونیک | پرسنل و منابع انسانی</t>
+          <t>خدمات مشتری و شخصی | ایمنی و امنیت عمومی | زبان انگلیسی | حمل و نقل | روان‌شناسی | جغرافیا | رایانه و الکترونیک | پرسنل و منابع انسانی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>بیان شفاهی | وضوح گفتار | درک شفاهی | تشخیص گفتار | حساسیت به مسئله | بینایی نزدیک | استدلال قیاسی | سازماندهی اطلاعات | توجه شنیداری | بینایی دور | انعطاف‌پذیری حرکتی | توجه انتخابی | سرعت ادراکی | استدلال استقرایی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | درک کتبی | تعادل کلی بدن | قدرت تنه</t>
+          <t>بیان شفاهی | وضوح گفتار | درک شفاهی | تشخیص گفتار | حساسیت به مسئله | بینایی نزدیک | استدلال قیاسی | ترتیب‌دهی اطلاعات | توجه شنیداری | بینایی دور | انعطاف‌پذیری دامنه حرکت | توجه انتخابی | سرعت ادراکی | استدلال استقرایی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | درک کتبی | تعادل کلی بدن | قدرت تنه</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>سلامت و ایمنی سایر کارکنان | سخنرانی عمومی | داخل ساختمان، محیط کنترل‌شده | برخورد با مشتریان خارجی یا عموم مردم به‌طور کلی | ارتباط با دیگران | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | نزدیکی فیزیکی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | فراوانی تصمیم‌گیری | کار با یا مشارکت در یک گروه یا تیم کاری | آزادی در تصمیم‌گیری | قرار گرفتن در معرض ارتفاعات بالا | تأثیر تصمیمات بر همکاران یا نتایج شرکت | پیامد خطا | فشار زمانی | ایمیل | قرار گرفتن در معرض آلاینده‌ها | موقعیت‌های تعارض | قرار گرفتن در معرض تابش | پیامدهای کاری و نتایج سایر کارکنان | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | اهمیت دقیق یا منظم بودن | صرف زمان به حالت ایستاده | قرار گرفتن در معرض بیماری یا عفونت‌ها | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان به پیاده‌روی یا دویدن | اهمیت تکرار وظایف مشابه | صرف زمان به خم شدن یا چرخاندن بدن</t>
+          <t>سلامت و ایمنی سایر کارکنان | سخنرانی عمومی | محیط داخلی، دارای کنترل شرایط محیطی | تعامل با مشتریان خارجی یا عموم مردم | ارتباط با دیگران | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | نزدیکی فیزیکی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | فراوانی تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | قرار گرفتن در معرض ارتفاعات بالا | تأثیر تصمیمات بر همکاران یا نتایج شرکت | پیامد خطا | فشار زمانی | ایمیل | قرار گرفتن در معرض آلاینده‌ها | موقعیت‌های تعارض | قرار گرفتن در معرض تابش | پیامدهای کاری و نتایج سایر کارکنان | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | اهمیت دقیق یا درست بودن | صرف زمان برای ایستادن | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای راه رفتن یا دویدن | اهمیت تکرار وظایف یکسان | صرف زمان برای خم کردن یا چرخاندن بدن</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>کنترل‌کنندگان ترافیک هوایی | سرپرستان جابجایی بار هواپیما | متصدیان خدمات هواپیما | متخصصان عملیات فرودگاه | خلبانان، کمک‌خلبانان و مهندسان پرواز خطوط هوایی | رانندگان و متصدیان آمبولانس، به‌جز تکنسین‌های فوریت‌های پزشکی | باربران چمدان و پادوها | رانندگان اتوبوس، ترانزیت و بین‌شهری | خلبانان تجاری | دیسپچرهای غیر از پلیس، آتش‌نشانی و آمبولانس | سرپرستان رده اول متصدیان مسافران | متصدیان رختکن و اتاق پرو | متصدیان مسافران | لوکوموتیورانان و مسئولان ایستگاه راه‌آهن | نمایندگان فروش بلیط و رزرواسیون حمل‌ونقل و کارمندان سفر | نگهبانان امنیتی | رانندگان شاتل و شوفرها | اپراتورهای مترو و تراموا | ماموران غربالگری امنیت حمل‌ونقل | راهنمایان سالن، متصدیان لابی و بلیط‌گیرها</t>
+          <t>کنترلرهای ترافیک هوایی | سرپرستان جابجایی بار هواپیما | متصدیان خدمات هواپیما | متخصصان عملیات فرودگاه | خلبانان، کمک‌خلبانان و مهندسان پرواز خطوط هوایی | رانندگان و متصدیان آمبولانس، به جز تکنسین‌های فوریت‌های پزشکی | باربران چمدان و پادوهای هتل | رانندگان اتوبوس، ترانزیت و بین‌شهری | خلبانان تجاری | دیسپچرهای غیر از پلیس، آتش‌نشانی و آمبولانس | سرپرستان خط اول مهمانداران مسافری | متصدیان رختکن، اتاق لباس و اتاق پرو | متصدیان مسافران | رئیس قطارها و مدیران محوطه راه‌آهن | نمایندگان بلیط و رزرواسیون حمل و نقل و کارمندان سفر | نگهبانان امنیتی | رانندگان شاتل و شوفرها | رانندگان مترو و تراموا | غربالگران امنیتی حمل و نقل | راهنماها، متصدیان لابی و بلیط‌گیرها</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -560,32 +560,32 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>نرم‌افزار دیسپچ به کمک کامپیوتر | نرم‌افزار نقشه‌برداری | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Word</t>
+          <t>نرم‌افزار اعزام به کمک کامپیوتر | نرم‌افزار نقشه‌برداری | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Word</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | گوش‌دادن فعال | درک مطلب | سخن‌گفتن | یادگیری فعال | مانیتورینگ</t>
+          <t>تفکر انتقادی | گوش دادن فعال | درک مطلب | سخن گفتن | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | زبان انگلیسی | ایمنی و امنیت عمومی | امور اداری و مدیریت | قانون و حکومت | حمل‌ونقل | آموزش و پرورش | پزشکی و دندانپزشکی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | ایمنی و امنیت عمومی | مدیریت و اداره | قانون و دولت | حمل و نقل | آموزش و پرورش | پزشکی و دندان‌پزشکی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | حساسیت به مسئله | بیان شفاهی | استدلال قیاسی | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | بینایی دور | قدرت ایستا | زمان واکنش | جهت‌گیری واکنش | هماهنگی چندعضوی | ثبات دست و بازو | تقسیم توجه | جهت‌گیری فضایی | سازماندهی اطلاعات | استدلال استقرایی | درک کتبی | چالاکی دست | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | درک عمق | قدرت تنه | دقت کنترل</t>
+          <t>درک شفاهی | حساسیت به مسئله | بیان شفاهی | استدلال قیاسی | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | بینایی دور | قدرت ایستا | زمان عکس‌العمل | جهت‌گیری پاسخ | هماهنگی چند عضو | ثبات دست و بازو | تقسیم توجه | جهت‌گیری فضایی | ترتیب‌دهی اطلاعات | استدلال استقرایی | درک کتبی | مهارت دستی | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | درک عمق | قدرت تنه | دقت کنترل</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>سلامت و ایمنی سایر کارکنان | ارتباط با دیگران | نزدیکی فیزیکی | اهمیت دقیق یا منظم بودن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | پوشیدن تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فضای باز، قرار گرفتن در معرض تمام شرایط آب‌وهوایی | کار با یا مشارکت در یک گروه یا تیم کاری | تعیین وظایف، اولویت‌ها و اهداف | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | آزادی در تصمیم‌گیری | برخورد با مشتریان خارجی یا عموم مردم به‌طور کلی | پیامد خطا | مکالمات تلفنی | قرار گرفتن در معرض بیماری یا عفونت‌ها | اهمیت تکرار وظایف مشابه | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فشار زمانی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | قرار گرفتن در معرض آلاینده‌ها | فضای باز، زیر سقف</t>
+          <t>سلامت و ایمنی سایر کارکنان | ارتباط با دیگران | نزدیکی فیزیکی | اهمیت دقیق یا درست بودن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فضای باز، در معرض تمام شرایط آب و هوایی | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | آزادی در تصمیم‌گیری | تعامل با مشتریان خارجی یا عموم مردم | پیامد خطا | مکالمات تلفنی | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | اهمیت تکرار وظایف یکسان | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فشار زمانی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | قرار گرفتن در معرض آلاینده‌ها | فضای باز، زیر سقف</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>پرستاران مراقبت‌های ویژه | دستیاران متخصص بیهوشی | دیسپچرهای غیر از پلیس، آتش‌نشانی و آمبولانس | مدیران مدیریت بحران | تکنسین‌های فوریت‌های پزشکی | پزشکان طب اورژانس | دستیاران سلامت در منزل | پرستاران عملیاتی مجاز و پرستاران حرفه‌ای مجاز | نجات‌غریق‌ها، گشت اسکی و سایر کارکنان خدمات حفاظتی تفریحی | دستیاران پزشکی | مدیران خدمات پزشکی و بهداشتی | کمک‌پرستاران | بهیاران | پارامدیک‌ها | دستیاران مراقبت شخصی | دستیاران فیزیوتراپی | اپراتورهای مخابراتی امنیت عمومی | پرستاران ثبت‌نام‌شده | دستیاران جراحی | تکنسین‌های جراحی</t>
+          <t>پرستاران مراقبت‌های ویژه | دستیاران متخصص بیهوشی | دیسپچرهای غیر از پلیس، آتش‌نشانی و آمبولانس | مدیران مدیریت بحران | تکنسین‌های فوریت‌های پزشکی | پزشکان طب اورژانس | کمک‌یاران سلامت در منزل | پرستاران عملی دارای مجوز و پرستاران حرفه‌ای دارای مجوز | نجات‌غریق‌ها، گشت اسکی و سایر کارکنان خدمات حفاظتی تفریحی | دستیاران پزشکی | مدیران خدمات پزشکی و بهداشتی | کمک‌پرستاران | بهیاران | پارامدیک‌ها | کمک‌یاران مراقبت شخصی | کمک‌یاران فیزیوتراپی | اپراتورهای مخابراتی امنیت عمومی | پرستاران ثبت‌شده | دستیاران جراحی | تکنولوژیست‌های جراحی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,27 +622,27 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>گوش‌دادن فعال | سخن‌گفتن | تفکر انتقادی | درک مطلب</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | درک مطلب</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | تولید مواد غذایی | زبان انگلیسی | حمل‌ونقل | ایمنی و امنیت عمومی | امور اداری و مدیریت</t>
+          <t>خدمات مشتری و شخصی | تولید مواد غذایی | زبان انگلیسی | حمل و نقل | ایمنی و امنیت عمومی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | حساسیت به مسئله | استدلال قیاسی | درک کتبی | بینایی دور | قدرت تنه | قدرت ایستا | دقت کنترل | چالاکی انگشتان | ثبات دست و بازو | انعطاف‌پذیری دسته‌بندی | سازماندهی اطلاعات | استدلال استقرایی</t>
+          <t>درک شفاهی | بیان شفاهی | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | حساسیت به مسئله | استدلال قیاسی | درک کتبی | بینایی دور | قدرت تنه | قدرت ایستا | دقت کنترل | مهارت انگشتان | ثبات دست و بازو | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>فضای باز، قرار گرفتن در معرض تمام شرایط آب‌وهوایی | فشار زمانی | قرار گرفتن در معرض دمای بسیار گرم یا سرد | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت تکرار وظایف مشابه | ارتباط با دیگران | برخورد با مشتریان خارجی یا عموم مردم به‌طور کلی | صرف زمان برای انجام حرکات تکراری | اهمیت دقیق یا منظم بودن | صرف زمان به خم شدن یا چرخاندن بدن | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان به پیاده‌روی یا دویدن | مکالمات تلفنی | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | تأثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان به حالت ایستاده | فراوانی تصمیم‌گیری | پوشیدن تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات</t>
+          <t>فضای باز، در معرض تمام شرایط آب و هوایی | فشار زمانی | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت تکرار وظایف یکسان | ارتباط با دیگران | تعامل با مشتریان خارجی یا عموم مردم | صرف زمان برای انجام حرکات تکراری | اهمیت دقیق یا درست بودن | صرف زمان برای خم کردن یا چرخاندن بدن | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای راه رفتن یا دویدن | مکالمات تلفنی | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | تأثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای ایستادن | فراوانی تصمیم‌گیری | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>خریداران و نمایندگان خرید، محصولات کشاورزی | نمایندگان بار و محموله | صندوقداران | کارمندان باجه و اجاره | پیک‌ها و نامه‌رسان‌ها | نمایندگان خدمات مشتریان | دیسپچرهای غیر از پلیس، آتش‌نشانی و آمبولانس | فروشندگان خانه‌به‌خانه، روزنامه‌فروشان دوره‌گرد و خیابانی، و کارکنان مرتبط | کارکنان فست‌فود و باجه | رانندگان کامیون‌های سنگین و تریلی | کارگران و جابجا‌کنندگان دستی بار، کالا و مواد | رانندگان کامیون‌های سبک | کارمندان ثبت سفارش | متصدیان پارکینگ | کارمندان اداره پست | نامه‌رسان‌های اداره پست | فروشندگان خرده‌فروشی | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و سفر | کارمندان ارسال، دریافت و انبارداری | انبارداران و پرکنندگان سفارش</t>
+          <t>خریداران و نمایندگان خرید، محصولات کشاورزی | نمایندگان بار و محموله | صندوق‌داران | کارمندان باجه و اجاره | پیک‌ها و نامه‌رسان‌ها | نمایندگان خدمات مشتریان | دیسپچرهای غیر از پلیس، آتش‌نشانی و آمبولانس | فروشندگان خانه‌به‌خانه، فروشندگان روزنامه و خیابانی و کارکنان مرتبط | کارگران فست فود و پیشخوان | رانندگان کامیون‌های سنگین و تریلی | کارگران و جابجا‌کنندگان دستی بار، کالا و مواد | رانندگان کامیون‌های سبک | کارمندان ثبت سفارش | متصدیان پارکینگ | کارمندان خدمات پستی | نامه‌رسان‌های خدمات پستی | فروشندگان خرده‌فروشی | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و سفر | کارمندان ارسال، دریافت و موجودی کالا | قفسه‌چین‌ها و پرکننده‌های سفارش</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,27 +679,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>مانیتورینگ | تفکر انتقادی | سخن‌گفتن | درک مطلب</t>
+          <t>نظارت | تفکر انتقادی | سخن گفتن | درک مطلب</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>حمل‌ونقل | ایمنی و امنیت عمومی | خدمات مشتریان و شخصی | زبان انگلیسی | قانون و حکومت</t>
+          <t>حمل و نقل | ایمنی و امنیت عمومی | خدمات مشتری و شخصی | زبان انگلیسی | قانون و دولت</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>بینایی دور | جهت‌گیری فضایی | دقت کنترل | هماهنگی چندعضوی | جهت‌گیری واکنش | کنترل سرعت | زمان واکنش | حساسیت به مسئله | بینایی نزدیک | درک عمق | توجه انتخابی | استدلال قیاسی | درک شفاهی | درک کتبی | حساسیت شنوایی | حساسیت به درخشندگی شدید | بینایی محیطی | بینایی در شب | قدرت ایستا | چالاکی دست | ثبات دست و بازو | تقسیم توجه | تجسم فضایی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | سازماندهی اطلاعات | بیان شفاهی | وضوح گفتار | تشخیص گفتار | توجه شنیداری</t>
+          <t>بینایی دور | جهت‌گیری فضایی | دقت کنترل | هماهنگی چند عضو | جهت‌گیری پاسخ | کنترل نرخ | زمان عکس‌العمل | حساسیت به مسئله | بینایی نزدیک | درک عمق | توجه انتخابی | استدلال قیاسی | درک شفاهی | درک کتبی | حساسیت شنوایی | حساسیت به درخشندگی شدید | بینایی محیطی | بینایی در شب | قدرت ایستا | مهارت دستی | ثبات دست و بازو | تقسیم توجه | تجسم | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | بیان شفاهی | وضوح گفتار | تشخیص گفتار | توجه شنیداری</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | فضای باز، قرار گرفتن در معرض تمام شرایط آب‌وهوایی | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای استفاده از دست‌ها جهت جابجایی, کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | پوشیدن تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | آزادی در تصمیم‌گیری | قرار گرفتن در معرض دمای بسیار گرم یا سرد | فشار زمانی | ارتباط با دیگران | صرف زمان به حالت نشسته | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | پیامد خطا | اهمیت دقیق یا منظم بودن | مکالمات تلفنی | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض آلاینده‌ها | برخورد با مشتریان خارجی یا عموم مردم به‌طور کلی | سلامت و ایمنی سایر کارکنان | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | کار با یا مشارکت در یک گروه یا تیم کاری | اهمیت تکرار وظایف مشابه</t>
+          <t>در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | فضای باز، در معرض تمام شرایط آب و هوایی | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | آزادی در تصمیم‌گیری | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | فشار زمانی | ارتباط با دیگران | صرف زمان برای نشستن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | پیامد خطا | اهمیت دقیق یا درست بودن | مکالمات تلفنی | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض آلاینده‌ها | تعامل با مشتریان خارجی یا عموم مردم | سلامت و ایمنی سایر کارکنان | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت تکرار وظایف یکسان</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>رانندگان اتوبوس، ترانزیت و بین‌شهری | مکانیک‌های اتوبوس و کامیون و متخصصان موتورهای دیزلی | اپراتورهای جرثقیل و تاورکرین | دیسپچرهای غیر از پلیس، آتش‌نشانی و آمبولانس | کارگران نگهداری بزرگراه‌ها | اپراتورهای بالابر و وینچ | اپراتورهای کامیون و تراکتور صنعتی | کارگران و جابجا‌کنندگان دستی بار، کالا و مواد | رانندگان کامیون‌های سبک | اپراتورهای ماشین‌آلات بارگیری و جابجایی، استخراج زیرزمینی | مهندسان لوکوموتیو | اپراتورهای ماشین‌آلات مهندسی و سایر تجهیزات ساخت‌وساز | اپراتورهای شمع‌کوب | مهندسان محوطه راه‌آهن، اپراتورهای دینکی و لوکوموتیورانان مانور | اپراتورهای ترمز، سیگنال و سوزن‌بان راه‌آهن و آتش‌نشانان لوکوموتیو | لوکوموتیورانان و مسئولان ایستگاه راه‌آهن | جمع‌آوری‌کنندگان زباله و مواد بازیافتی | رانندگان شاتل و شوفرها | بارگیران واگن‌های مخزن‌دار، کامیون‌ها و کشتی‌ها | رانندگان تاکسی</t>
+          <t>رانندگان اتوبوس، ترانزیت و بین‌شهری | مکانیک‌های اتوبوس و کامیون و متخصصان موتورهای دیزلی | اپراتورهای جرثقیل و تاور | دیسپچرهای غیر از پلیس، آتش‌نشانی و آمبولانس | کارگران نگهداری بزرگراه‌ها | اپراتورهای بالابر و وینچ | اپراتورهای تراکتور و کامیون صنعتی | کارگران و جابجا‌کنندگان دستی بار، کالا و مواد | رانندگان کامیون‌های سبک | اپراتورهای ماشین‌های بارگیری و انتقال، معدن‌کاری زیرزمینی | مهندسان لوکوموتیو | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | اپراتورهای کوبنده شمع | مهندسان محوطه راه‌آهن، اپراتورهای لکوموتیو مانوری و متصدیان آماده‌سازی لکوموتیو | اپراتورهای ترمز، علائم و سوزن راه‌آهن و آتش‌کاران لکوموتیو | رئیس قطارها و مدیران محوطه راه‌آهن | جمع‌آوران زباله و مواد بازیافتی | رانندگان شاتل و شوفرها | بارگیران واگن مخزنی، کامیون و کشتی | رانندگان تاکسی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -731,32 +731,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>نرم‌افزار مسیریابی خودکار | نرم‌افزار ردیابی موجودی کامپیوتری | Eko | FreightDATA | IBM Domino | سیستم‌های مدیریت موجودی | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Windows | نرم‌افزار مکان‌یابی و ردیابی بسته | نرم‌افزار بایگانی سوابق | نرم‌افزار مکان‌یابی و ردیابی وسیله نقلیه</t>
+          <t>نرم‌افزار مسیریابی خودکار | نرم‌افزار ردیابی موجودی کامپیوتری | Eko | FreightDATA | IBM Domino | سیستم‌های مدیریت موجودی | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Windows | نرم‌افزار مکان‌یابی و ردیابی بسته | نرم‌افزار ثبت سوابق | نرم‌افزار مکان‌یابی و ردیابی وسیله نقلیه</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>گوش‌دادن فعال | سخن‌گفتن | مانیتورینگ | درک مطلب | تفکر انتقادی</t>
+          <t>گوش دادن فعال | سخن گفتن | نظارت | درک مطلب | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | حمل‌ونقل | خدمات مشتریان و شخصی</t>
+          <t>زبان انگلیسی | حمل و نقل | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>هماهنگی چندعضوی | بینایی دور | جهت‌گیری فضایی | حساسیت به مسئله | بینایی نزدیک | استقامت | قدرت تنه | قدرت ایستا | زمان واکنش | دقت کنترل | چالاکی دست | استدلال قیاسی | بیان شفاهی | درک شفاهی | درک کتبی | انعطاف‌پذیری حرکتی | جهت‌گیری واکنش | سرعت ادراکی | سازماندهی اطلاعات | استدلال استقرایی | وضوح گفتار | تشخیص گفتار | درک عمق</t>
+          <t>هماهنگی چند عضو | بینایی دور | جهت‌گیری فضایی | حساسیت به مسئله | بینایی نزدیک | استقامت | قدرت تنه | قدرت ایستا | زمان عکس‌العمل | دقت کنترل | مهارت دستی | استدلال قیاسی | بیان شفاهی | درک شفاهی | درک کتبی | انعطاف‌پذیری دامنه حرکت | جهت‌گیری پاسخ | سرعت ادراکی | ترتیب‌دهی اطلاعات | استدلال استقرایی | وضوح گفتار | تشخیص گفتار | درک عمق</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | ارتباط با دیگران | اهمیت دقیق یا منظم بودن | مکالمات تلفنی | فشار زمانی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فضای باز، قرار گرفتن در معرض تمام شرایط آب‌وهوایی | برخورد با مشتریان خارجی یا عموم مردم به‌طور کلی | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان به حالت نشسته</t>
+          <t>در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | ارتباط با دیگران | اهمیت دقیق یا درست بودن | مکالمات تلفنی | فشار زمانی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فضای باز، در معرض تمام شرایط آب و هوایی | تعامل با مشتریان خارجی یا عموم مردم | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای نشستن</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>رانندگان اتوبوس، ترانزیت و بین‌شهری | نمایندگان بار و محموله | پیک‌ها و نامه‌رسان‌ها | دیسپچرهای غیر از پلیس، آتش‌نشانی و آمبولانس | رانندگان توزیع و فروشندگان | سرپرستان رده اول اپراتورهای ماشین‌آلات جابجایی مواد و وسایل نقلیه | رانندگان کامیون‌های سنگین و تریلی | اپراتورهای کامیون و تراکتور صنعتی | متصدیان پارکینگ | کارمندان اداره پست | نامه‌رسان‌های اداره پست | لوکوموتیورانان و مسئولان ایستگاه راه‌آهن | جمع‌آوری‌کنندگان زباله و مواد بازیافتی | کارمندان ارسال، دریافت و انبارداری | رانندگان شاتل و شوفرها | انبارداران و پرکنندگان سفارش | بارگیران واگن‌های مخزن‌دار، کامیون‌ها و کشتی‌ها | رانندگان تاکسی | بازرسان حمل‌ونقل | بازرسان وسایل نقلیه، تجهیزات و سیستم‌های حمل‌ونقل، به جز هوانوردی</t>
+          <t>رانندگان اتوبوس، ترانزیت و بین‌شهری | نمایندگان بار و محموله | پیک‌ها و نامه‌رسان‌ها | دیسپچرهای غیر از پلیس، آتش‌نشانی و آمبولانس | رانندگان توزیع و فروشندگان | سرپرستان خط اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابجایی مواد | رانندگان کامیون‌های سنگین و تریلی | اپراتورهای تراکتور و کامیون صنعتی | متصدیان پارکینگ | کارمندان خدمات پستی | نامه‌رسان‌های خدمات پستی | رئیس قطارها و مدیران محوطه راه‌آهن | جمع‌آوران زباله و مواد بازیافتی | کارمندان ارسال، دریافت و موجودی کالا | رانندگان شاتل و شوفرها | قفسه‌چین‌ها و پرکننده‌های سفارش | بارگیران واگن مخزنی، کامیون و کشتی | رانندگان تاکسی | بازرسان حمل‌ونقل | بازرسان وسایل نقلیه، تجهیزات و سیستم‌های حمل‌ونقل، به جز هوانوردی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,27 +793,27 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>گوش‌دادن فعال | تفکر انتقادی | مانیتورینگ | سخن‌گفتن | درک مطلب</t>
+          <t>گوش دادن فعال | تفکر انتقادی | نظارت | سخن گفتن | درک مطلب</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>حمل‌ونقل | ایمنی و امنیت عمومی | خدمات مشتریان و شخصی | زبان انگلیسی | مکانیک | قانون و حکومت | جغرافیا</t>
+          <t>حمل و نقل | ایمنی و امنیت عمومی | خدمات مشتری و شخصی | زبان انگلیسی | مکانیک | قانون و دولت | جغرافیا</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>بینایی دور | بینایی نزدیک | زمان واکنش | حساسیت به مسئله | درک عمق | تشخیص گفتار | بینایی محیطی | هماهنگی چندعضوی | دقت کنترل | توجه شنیداری | درک شفاهی | جهت‌گیری فضایی | وضوح گفتار | تشخیص رنگ‌های بصری | کنترل سرعت | جهت‌گیری واکنش | ثبات دست و بازو | تقسیم توجه | توجه انتخابی | سازماندهی اطلاعات | بیان شفاهی | استدلال قیاسی</t>
+          <t>بینایی دور | بینایی نزدیک | زمان عکس‌العمل | حساسیت به مسئله | درک عمق | تشخیص گفتار | بینایی محیطی | هماهنگی چند عضو | دقت کنترل | توجه شنیداری | درک شفاهی | جهت‌گیری فضایی | وضوح گفتار | تشخیص رنگ بصری | کنترل نرخ | جهت‌گیری پاسخ | ثبات دست و بازو | تقسیم توجه | توجه انتخابی | ترتیب‌دهی اطلاعات | بیان شفاهی | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | فراوانی تصمیم‌گیری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان به حالت نشسته | ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا منظم بودن | آزادی در تصمیم‌گیری | نزدیکی فیزیکی | فضای باز، قرار گرفتن در معرض تمام شرایط آب‌وهوایی | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | صرف زمان برای انجام حرکات تکراری | فشار زمانی | سلامت و ایمنی سایر کارکنان | تأثیر تصمیمات بر همکاران یا نتایج شرکت | پیامد خطا</t>
+          <t>در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | فراوانی تصمیم‌گیری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای نشستن | ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | آزادی در تصمیم‌گیری | نزدیکی فیزیکی | فضای باز، در معرض تمام شرایط آب و هوایی | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | صرف زمان برای انجام حرکات تکراری | فشار زمانی | سلامت و ایمنی سایر کارکنان | تأثیر تصمیمات بر همکاران یا نتایج شرکت | پیامد خطا</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>کنترل‌کنندگان ترافیک هوایی | رانندگان و متصدیان آمبولانس، به‌جز تکنسین‌های فوریت‌های پزشکی | رانندگان اتوبوس، ترانزیت و بین‌شهری | خلبانان تجاری | ماموران عبور و پرچم‌داران | دیسپچرهای غیر از پلیس، آتش‌نشانی و آمبولانس | تکنسین‌های فوریت‌های پزشکی | رانندگان کامیون‌های سنگین و تریلی | رانندگان کامیون‌های سبک | مهندسان لوکوموتیو | ماموران اجرای قانون پارکینگ | متصدیان مسافران | مهندسان محوطه راه‌آهن، اپراتورهای دینکی و لوکوموتیورانان مانور | اپراتورهای ترمز، سیگنال و سوزن‌بان راه‌آهن و آتش‌نشانان لوکوموتیو | لوکوموتیورانان و مسئولان ایستگاه راه‌آهن | ناظران اتوبوس مدرسه | رانندگان شاتل و شوفرها | اپراتورهای مترو و تراموا | رانندگان تاکسی | پلیس ترانزیت و راه‌آهن</t>
+          <t>کنترلرهای ترافیک هوایی | رانندگان و متصدیان آمبولانس، به جز تکنسین‌های فوریت‌های پزشکی | رانندگان اتوبوس، ترانزیت و بین‌شهری | خلبانان تجاری | نگهبانان عبور و مرور و پرچم‌داران | دیسپچرهای غیر از پلیس، آتش‌نشانی و آمبولانس | تکنسین‌های فوریت‌های پزشکی | رانندگان کامیون‌های سنگین و تریلی | رانندگان کامیون‌های سبک | مهندسان لوکوموتیو | ماموران اجرای مقررات پارک | متصدیان مسافران | مهندسان محوطه راه‌آهن، اپراتورهای لکوموتیو مانوری و متصدیان آماده‌سازی لکوموتیو | اپراتورهای ترمز، علائم و سوزن راه‌آهن و آتش‌کاران لکوموتیو | رئیس قطارها و مدیران محوطه راه‌آهن | مراقبین اتوبوس مدرسه | رانندگان شاتل و شوفرها | رانندگان مترو و تراموا | رانندگان تاکسی | پلیس ترانزیت و راه‌آهن</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,27 +850,27 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>گوش‌دادن فعال | تفکر انتقادی | سخن‌گفتن | مانیتورینگ</t>
+          <t>گوش دادن فعال | تفکر انتقادی | سخن گفتن | نظارت</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>حمل‌ونقل | خدمات مشتریان و شخصی | ایمنی و امنیت عمومی | زبان انگلیسی | قانون و حکومت</t>
+          <t>حمل و نقل | خدمات مشتری و شخصی | ایمنی و امنیت عمومی | زبان انگلیسی | قانون و دولت</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>بینایی دور | دقت کنترل | هماهنگی چندعضوی | درک عمق | جهت‌گیری واکنش | زمان واکنش | جهت‌گیری فضایی | بینایی نزدیک | کنترل سرعت | حساسیت به مسئله | توجه انتخابی | وضوح گفتار | درک شفاهی | بیان شفاهی | تقسیم توجه | بینایی محیطی | تشخیص گفتار | توجه شنیداری | ثبات دست و بازو | درک کتبی | حساسیت به درخشندگی شدید | بینایی در شب | سازماندهی اطلاعات | استدلال قیاسی</t>
+          <t>بینایی دور | دقت کنترل | هماهنگی چند عضو | درک عمق | جهت‌گیری پاسخ | زمان عکس‌العمل | جهت‌گیری فضایی | بینایی نزدیک | کنترل نرخ | حساسیت به مسئله | توجه انتخابی | وضوح گفتار | درک شفاهی | بیان شفاهی | تقسیم توجه | بینایی محیطی | تشخیص گفتار | توجه شنیداری | ثبات دست و بازو | درک کتبی | حساسیت به درخشندگی شدید | بینایی در شب | ترتیب‌دهی اطلاعات | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>صرف زمان به حالت نشسته | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | ارتباط با دیگران | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | نزدیکی فیزیکی | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | پیامد خطا | صرف زمان برای انجام حرکات تکراری | برخورد با مشتریان خارجی یا عموم مردم به‌طور کلی | فشار زمانی | اهمیت دقیق یا منظم بودن | آزادی در تصمیم‌گیری | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | قرار گرفتن در معرض آلاینده‌ها</t>
+          <t>صرف زمان برای نشستن | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | ارتباط با دیگران | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | نزدیکی فیزیکی | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | پیامد خطا | صرف زمان برای انجام حرکات تکراری | تعامل با مشتریان خارجی یا عموم مردم | فشار زمانی | اهمیت دقیق یا درست بودن | آزادی در تصمیم‌گیری | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | قرار گرفتن در معرض آلاینده‌ها</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>کنترل‌کنندگان ترافیک هوایی | متخصصان عملیات فرودگاه | باربران چمدان و پادوها | رانندگان اتوبوس، مدرسه | دیسپچرهای غیر از پلیس، آتش‌نشانی و آمبولانس | مهمانداران هواپیما | رانندگان کامیون‌های سنگین و تریلی | رانندگان کامیون‌های سبک | مهندسان لوکوموتیو | متصدیان پارکینگ | متصدیان مسافران | مهندسان محوطه راه‌آهن، اپراتورهای دینکی و لوکوموتیورانان مانور | اپراتورهای ترمز، سیگنال و سوزن‌بان راه‌آهن و آتش‌نشانان لوکوموتیو | لوکوموتیورانان و مسئولان ایستگاه راه‌آهن | نمایندگان فروش بلیط و رزرواسیون حمل‌ونقل و کارمندان سفر | ناظران اتوبوس مدرسه | رانندگان شاتل و شوفرها | اپراتورهای مترو و تراموا | رانندگان تاکسی | پلیس ترانزیت و راه‌آهن</t>
+          <t>کنترلرهای ترافیک هوایی | متخصصان عملیات فرودگاه | باربران چمدان و پادوهای هتل | رانندگان اتوبوس مدرسه | دیسپچرهای غیر از پلیس، آتش‌نشانی و آمبولانس | مهمانداران هواپیما | رانندگان کامیون‌های سنگین و تریلی | رانندگان کامیون‌های سبک | مهندسان لوکوموتیو | متصدیان پارکینگ | متصدیان مسافران | مهندسان محوطه راه‌آهن، اپراتورهای لکوموتیو مانوری و متصدیان آماده‌سازی لکوموتیو | اپراتورهای ترمز، علائم و سوزن راه‌آهن و آتش‌کاران لکوموتیو | رئیس قطارها و مدیران محوطه راه‌آهن | نمایندگان بلیط و رزرواسیون حمل و نقل و کارمندان سفر | مراقبین اتوبوس مدرسه | رانندگان شاتل و شوفرها | رانندگان مترو و تراموا | رانندگان تاکسی | پلیس ترانزیت و راه‌آهن</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,27 +907,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>گوش‌دادن فعال | مانیتورینگ | تفکر انتقادی | سخن‌گفتن</t>
+          <t>گوش دادن فعال | نظارت | تفکر انتقادی | سخن گفتن</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | حمل‌ونقل | ایمنی و امنیت عمومی | زبان انگلیسی | پرسنل و منابع انسانی | اداری | امور اداری و مدیریت | آموزش و پرورش | تولید و فرآوری | قانون و حکومت | روان‌شناسی | اقتصاد و حسابداری | ارتباطات و رسانه | ریاضیات | بازاریابی و فروش</t>
+          <t>خدمات مشتری و شخصی | حمل و نقل | ایمنی و امنیت عمومی | زبان انگلیسی | پرسنل و منابع انسانی | اداری | مدیریت و اداره | آموزش و پرورش | تولید و فرآوری | قانون و دولت | روان‌شناسی | اقتصاد و حسابداری | ارتباطات و رسانه | ریاضیات | فروش و بازاریابی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | بینایی دور | هماهنگی چندعضوی | دقت کنترل | حساسیت به مسئله | درک شفاهی | درک عمق | وضوح گفتار | جهت‌گیری فضایی | توجه انتخابی | کنترل سرعت | زمان واکنش | تشخیص گفتار | بینایی محیطی | ثبات دست و بازو | تقسیم توجه | سازماندهی اطلاعات | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | جهت‌گیری واکنش | سرعت ادراکی | توجه شنیداری | بینایی در شب</t>
+          <t>بینایی نزدیک | بینایی دور | هماهنگی چند عضو | دقت کنترل | حساسیت به مسئله | درک شفاهی | درک عمق | وضوح گفتار | جهت‌گیری فضایی | توجه انتخابی | کنترل نرخ | زمان عکس‌العمل | تشخیص گفتار | بینایی محیطی | ثبات دست و بازو | تقسیم توجه | ترتیب‌دهی اطلاعات | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | جهت‌گیری پاسخ | سرعت ادراکی | توجه شنیداری | بینایی در شب</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | نزدیکی فیزیکی | برخورد با مشتریان خارجی یا عموم مردم به‌طور کلی | فضای باز، قرار گرفتن در معرض تمام شرایط آب‌وهوایی | ارتباط با دیگران | فشار زمانی | اهمیت دقیق یا منظم بودن | آزادی در تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | پیامد خطا | صرف زمان به حالت نشسته | فراوانی تصمیم‌گیری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | کار با یا مشارکت در یک گروه یا تیم کاری | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | سلامت و ایمنی سایر کارکنان</t>
+          <t>در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | نزدیکی فیزیکی | تعامل با مشتریان خارجی یا عموم مردم | فضای باز، در معرض تمام شرایط آب و هوایی | ارتباط با دیگران | فشار زمانی | اهمیت دقیق یا درست بودن | آزادی در تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | پیامد خطا | صرف زمان برای نشستن | فراوانی تصمیم‌گیری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | سلامت و ایمنی سایر کارکنان</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>باربران چمدان و پادوها | رانندگان اتوبوس، مدرسه | رانندگان اتوبوس، ترانزیت و بین‌شهری | مکانیک‌های اتوبوس و کامیون و متخصصان موتورهای دیزلی | پیک‌ها و نامه‌رسان‌ها | دیسپچرهای غیر از پلیس، آتش‌نشانی و آمبولانس | رانندگان توزیع و فروشندگان | رانندگان کامیون‌های سنگین و تریلی | اپراتورهای کامیون و تراکتور صنعتی | رانندگان کامیون‌های سبک | اپراتورهای ماشین‌آلات بارگیری و جابجایی، استخراج زیرزمینی | مهندسان لوکوموتیو | متصدیان پارکینگ | متصدیان مسافران | تعمیرکاران واگن‌های ریلی | لوکوموتیورانان و مسئولان ایستگاه راه‌آهن | نمایندگان فروش بلیط و رزرواسیون حمل‌ونقل و کارمندان سفر | اپراتورهای مترو و تراموا | رانندگان تاکسی | بازرسان وسایل نقلیه، تجهیزات و سیستم‌های حمل‌ونقل، به جز هوانوردی</t>
+          <t>باربران چمدان و پادوهای هتل | رانندگان اتوبوس مدرسه | رانندگان اتوبوس، ترانزیت و بین‌شهری | مکانیک‌های اتوبوس و کامیون و متخصصان موتورهای دیزلی | پیک‌ها و نامه‌رسان‌ها | دیسپچرهای غیر از پلیس، آتش‌نشانی و آمبولانس | رانندگان توزیع و فروشندگان | رانندگان کامیون‌های سنگین و تریلی | اپراتورهای تراکتور و کامیون صنعتی | رانندگان کامیون‌های سبک | اپراتورهای ماشین‌های بارگیری و انتقال، معدن‌کاری زیرزمینی | مهندسان لوکوموتیو | متصدیان پارکینگ | متصدیان مسافران | تعمیرکنندگان واگن‌های ریلی | رئیس قطارها و مدیران محوطه راه‌آهن | نمایندگان بلیط و رزرواسیون حمل و نقل و کارمندان سفر | رانندگان مترو و تراموا | رانندگان تاکسی | بازرسان وسایل نقلیه، تجهیزات و سیستم‌های حمل‌ونقل، به جز هوانوردی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,27 +964,27 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>مانیتورینگ | گوش‌دادن فعال | تفکر انتقادی | درک مطلب | سخن‌گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>حمل‌ونقل | خدمات مشتریان و شخصی | جغرافیا | زبان انگلیسی | ایمنی و امنیت عمومی | قانون و حکومت | ریاضیات</t>
+          <t>حمل و نقل | خدمات مشتری و شخصی | جغرافیا | زبان انگلیسی | ایمنی و امنیت عمومی | قانون و دولت | ریاضیات</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>چالاکی دست | چالاکی انگشتان | ثبات دست و بازو | هماهنگی چندعضوی | دقت کنترل | قدرت ایستا | قدرت تنه | استقامت | بینایی نزدیک | بینایی دور | درک عمق | هماهنگی کلی بدن | تعادل کلی بدن | انعطاف‌پذیری حرکتی | زمان واکنش | حساسیت به مسئله | درک شفاهی | توجه انتخابی | بیان شفاهی | وضوح گفتار | جهت‌گیری فضایی | تقسیم توجه</t>
+          <t>مهارت دستی | مهارت انگشتان | ثبات دست و بازو | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | قدرت تنه | استقامت | بینایی نزدیک | بینایی دور | درک عمق | هماهنگی کلی بدن | تعادل کلی بدن | انعطاف‌پذیری دامنه حرکت | زمان عکس‌العمل | حساسیت به مسئله | درک شفاهی | توجه انتخابی | بیان شفاهی | وضوح گفتار | جهت‌گیری فضایی | تقسیم توجه</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | صرف زمان به حالت نشسته | قرار گرفتن در معرض ارتعاش کل بدن | قرار گرفتن در معرض آلاینده‌ها | پیامد خطا | اهمیت دقیق یا منظم بودن | سلامت و ایمنی سایر کارکنان | فضای باز، قرار گرفتن در معرض تمام شرایط آب‌وهوایی | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | قرار گرفتن در معرض دمای بسیار گرم یا سرد | آزادی در تصمیم‌گیری | فراوانی تصمیم‌گیری | ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | فشار زمانی | برخورد با مشتریان خارجی یا عموم مردم به‌طور کلی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | نزدیکی فیزیکی</t>
+          <t>در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | صرف زمان برای نشستن | قرار گرفتن در معرض ارتعاش کل بدن | قرار گرفتن در معرض آلاینده‌ها | پیامد خطا | اهمیت دقیق یا درست بودن | سلامت و ایمنی سایر کارکنان | فضای باز، در معرض تمام شرایط آب و هوایی | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | آزادی در تصمیم‌گیری | فراوانی تصمیم‌گیری | ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | فشار زمانی | تعامل با مشتریان خارجی یا عموم مردم | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | نزدیکی فیزیکی</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>رانندگان اتوبوس، مدرسه | رانندگان اتوبوس، ترانزیت و بین‌شهری | مکانیک‌های اتوبوس و کامیون و متخصصان موتورهای دیزلی | پیک‌ها و نامه‌رسان‌ها | دیسپچرهای غیر از پلیس, آتش‌نشانی و آمبولانس | رانندگان توزیع و فروشندگان | رانندگان کامیون‌های سنگین و تریلی | اپراتورهای کامیون و تراکتور صنعتی | رانندگان کامیون‌های سبک | اپراتورهای ماشین‌آلات بارگیری و جابجایی، استخراج زیرزمینی | مهندسان لوکوموتیو | متصدیان پارکینگ | متصدیان مسافران | تعمیرکاران واگن‌های ریلی | مهندسان محوطه راه‌آهن، اپراتورهای دینکی و لوکوموتیورانان مانور | اپراتورهای ترمز، سیگنال و سوزن‌بان راه‌آهن و آتش‌نشانان لوکوموتیو | لوکوموتیورانان و مسئولان ایستگاه راه‌آهن | رانندگان شاتل و شوفرها | اپراتورهای مترو و تراموا | بازرسان وسایل نقلیه، تجهیزات و سیستم‌های حمل‌ونقل، به جز هوانوردی</t>
+          <t>رانندگان اتوبوس مدرسه | رانندگان اتوبوس، ترانزیت و بین‌شهری | مکانیک‌های اتوبوس و کامیون و متخصصان موتورهای دیزلی | پیک‌ها و نامه‌رسان‌ها | دیسپچرهای غیر از پلیس، آتش‌نشانی و آمبولانس | رانندگان توزیع و فروشندگان | رانندگان کامیون‌های سنگین و تریلی | اپراتورهای تراکتور و کامیون صنعتی | رانندگان کامیون‌های سبک | اپراتورهای ماشین‌های بارگیری و انتقال، معدن‌کاری زیرزمینی | مهندسان لوکوموتیو | متصدیان پارکینگ | متصدیان مسافران | تعمیرکنندگان واگن‌های ریلی | مهندسان محوطه راه‌آهن، اپراتورهای لکوموتیو مانوری و متصدیان آماده‌سازی لکوموتیو | اپراتورهای ترمز، علائم و سوزن راه‌آهن و آتش‌کاران لکوموتیو | رئیس قطارها و مدیران محوطه راه‌آهن | رانندگان شاتل و شوفرها | رانندگان مترو و تراموا | بازرسان وسایل نقلیه، تجهیزات و سیستم‌های حمل‌ونقل، به جز هوانوردی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1016,32 +1016,32 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>نرم‌افزار مدیریت ناوگان | نرم‌افزار مدیریت حمل‌ونقل | سیستم مدیریت انبار WMS | Microsoft Excel | Microsoft Word | نرم‌افزار ایمیل | سیستم‌های مدیریت موجودی | نرم‌افزار پایگاه داده | نرم‌افزار برنامه‌ریزی | نرم‌افزار مرورگر وب | Microsoft Outlook | سیستم برنامه‌ریزی منابع سازمانی ERP</t>
+          <t>نرم‌افزار مدیریت ناوگان | نرم‌افزار مدیریت حمل و نقل | سیستم مدیریت انبار WMS | Microsoft Excel | Microsoft Word | نرم‌افزار ایمیل | سیستم‌های مدیریت موجودی | نرم‌افزار پایگاه داده | نرم‌افزار زمان‌بندی | نرم‌افزار مرورگر وب | Microsoft Outlook | سیستم برنامه‌ریزی منابع سازمانی ERP</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>مانیتورینگ | گوش‌دادن فعال | تفکر انتقادی | درک مطلب | سخن‌گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>حمل‌ونقل | ایمنی و امنیت عمومی | خدمات مشتریان و شخصی | زبان انگلیسی | جغرافیا | مکانیک | قانون و حکومت</t>
+          <t>حمل و نقل | ایمنی و امنیت عمومی | خدمات مشتری و شخصی | زبان انگلیسی | جغرافیا | مکانیک | قانون و دولت</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>چالاکی دست | چالاکی انگشتان | ثبات دست و بازو | هماهنگی چندعضوی | دقت کنترل | قدرت ایستا | قدرت تنه | استقامت | بینایی نزدیک | بینایی دور | درک عمق | هماهنگی کلی بدن | تعادل کلی بدن | انعطاف‌پذیری حرکتی | زمان واکنش | حساسیت به مسئله | درک شفاهی | توجه انتخابی</t>
+          <t>مهارت دستی | مهارت انگشتان | ثبات دست و بازو | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | قدرت تنه | استقامت | بینایی نزدیک | بینایی دور | درک عمق | هماهنگی کلی بدن | تعادل کلی بدن | انعطاف‌پذیری دامنه حرکت | زمان عکس‌العمل | حساسیت به مسئله | درک شفاهی | توجه انتخابی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | صرف زمان به حالت نشسته | قرار گرفتن در معرض ارتعاش کل بدن | قرار گرفتن در معرض آلاینده‌ها | پیامد خطا | اهمیت دقیق یا منظم بودن | سلامت و ایمنی سایر کارکنان | فضای باز، قرار گرفتن در معرض تمام شرایط آب‌وهوایی | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | قرار گرفتن در معرض دمای بسیار گرم یا سرد | آزادی در تصمیم‌گیری | فراوانی تصمیم‌گیری | ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | فشار زمانی</t>
+          <t>در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | صرف زمان برای نشستن | قرار گرفتن در معرض ارتعاش کل بدن | قرار گرفتن در معرض آلاینده‌ها | پیامد خطا | اهمیت دقیق یا درست بودن | سلامت و ایمنی سایر کارکنان | فضای باز، در معرض تمام شرایط آب و هوایی | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | آزادی در تصمیم‌گیری | فراوانی تصمیم‌گیری | ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | فشار زمانی</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>رانندگان کامیون‌های سنگین و تریلی | رانندگان کامیون‌های سبک | رانندگان توزیع و فروشندگان | رانندگان شاتل و شوفرها | رانندگان تاکسی | رانندگان اتوبوس، مدرسه | رانندگان اتوبوس، ترانزیت و بین‌شهری | رانندگان و متصدیان آمبولانس، به‌جز تکنسین‌های فوریت‌های پزشکی | اپراتورهای کامیون و تراکتور صنعتی | متصدیان پارکینگ | متصدیان خدمات خودرو و شناورها | کارگران و جابجا‌کنندگان دستی بار، کالا و مواد | جمع‌آوری‌کنندگان زباله و مواد بازیافتی | پیک‌ها و نامه‌رسان‌ها | نمایندگان بار و محموله | دیسپچرهای غیر از پلیس، آتش‌نشانی و آمبولانس | بازرسان حمل‌ونقل | سرپرستان رده اول کارکنان حمل‌ونقل، سایر | مدیران حمل‌ونقل، انبارداری و توزیع | اپراتورهای جرثقیل و تاورکرین</t>
+          <t>رانندگان کامیون‌های سنگین و تریلی | رانندگان کامیون‌های سبک | رانندگان توزیع و فروشندگان | رانندگان شاتل و شوفرها | رانندگان تاکسی | رانندگان اتوبوس مدرسه | رانندگان اتوبوس، ترانزیت و بین‌شهری | رانندگان و متصدیان آمبولانس، به جز تکنسین‌های فوریت‌های پزشکی | اپراتورهای تراکتور و کامیون صنعتی | متصدیان پارکینگ | متصدیان خدمات خودرو و شناورهای آبی | کارگران و جابجا‌کنندگان دستی بار، کالا و مواد | جمع‌آوران زباله و مواد بازیافتی | پیک‌ها و نامه‌رسان‌ها | نمایندگان بار و محموله | دیسپچرهای غیر از پلیس، آتش‌نشانی و آمبولانس | بازرسان حمل‌ونقل | سرپرستان خط اول کارگران حمل و نقل، سایر | مدیران حمل‌ونقل، انبارداری و توزیع | اپراتورهای جرثقیل و تاور</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0096_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0096_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | نظارت | درک مطلب | تفکر انتقادی | یادگیری فعال | نگارش</t>
+          <t>سخن گفتن | گوش دادن فعال | نظارت | درک مطلب | تفکر انتقادی | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | ایمنی و امنیت عمومی | زبان انگلیسی | ترابری | روان‌شناسی | جغرافیا | رایانه و الکترونیک | پرسنلی و منابع انسانی</t>
+          <t>خدمات مشتری و شخصی | ایمنی و امنیت عمومی | زبان انگلیسی | حمل و نقل | روان‌شناسی | جغرافیا | رایانه و الکترونیک | پرسنل و منابع انسانی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>بیان شفاهی | وضوح گفتار | درک شفاهی | تشخیص گفتار | حساسیت به مسئله | دید نزدیک | استدلال قیاسی | مرتب‌سازی اطلاعات | توجه شنیداری | دید دور | انعطاف‌پذیری کششی | توجه انتخابی | سرعت ادراک | استدلال استقرایی | انعطاف‌پذیری در جمع‌بندی | انعطاف‌پذیری طبقه‌بندی | درک کتبی | تعادل عمومی بدن | قدرت عضلات تنه</t>
+          <t>بیان شفاهی | وضوح گفتار | درک شفاهی | تشخیص گفتار | حساسیت به مسئله | بینایی نزدیک | استدلال قیاسی | ترتیب‌دهی اطلاعات | توجه شنیداری | بینایی دور | انعطاف‌پذیری دامنه حرکت | توجه انتخابی | سرعت ادراکی | استدلال استقرایی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | درک کتبی | تعادل کلی بدن | قدرت تنه</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>کنترلرهای ترافیک هوایی | سرپرستان بارگیری و جابه‌جایی بار هواپیما | متصدیان خدمات زمینی هواپیما | کارشناسان عملیات فرودگاهی | خلبانان، کمک‌خلبانان و مهندسان پرواز خطوط هوایی | رانندگان و خدمه آمبولانس (به‌جز تکنسین‌های فوریت‌های پزشکی) | باربران فرودگاه و هتل | رانندگان اتوبوس‌های درون‌شهری و برون‌شهری | خلبانان تجاری | دیسپچرها (به‌جز پلیس، آتش‌نشانی و آمبولانس) | سرپرستان رده اول خدمه پذیرایی و تشریفات | متصدیان رختکن، امانات و اتاق‌های پرو | خدمه و مهمانداران مسافری | رئیسان قطار و مسئولان محوطه راه‌آهن | متصدیان رزرو، صدور بلیط و کارمندان آژانس‌های مسافرتی | ماموران حراست و نگهبانان | رانندگان خودروهای سرویس و رانندگان اختصاصی | راهبران مترو و تراموا | ماموران بازرسی و گیت‌های امنیتی ترابری | متصدیان پذیرش، راهنمایان سالن و باجه‌داران سینما و تئاتر</t>
+          <t>کنترلرهای ترافیک هوایی | سرپرستان بارگیری و جابه‌جایی بار هواپیما | متصدیان خدمات زمینی و سوخت‌رسانی فرودگاهی | کارشناسان عملیات فرودگاهی | خلبانان خطوط هوایی، کمک‌خلبانان و مهندسان پرواز | رانندگان و خدمه آمبولانس، به‌جز تکنسین‌های فوریت‌های پزشکی | متصدیان حمل بار و خدمات هتل | رانندگان اتوبوس‌های درون‌شهری و برون‌شهری | خلبانان تجاری | متصدیان دیسپاچ و اعزام | سرپرستان رده‌اول مهمانداران و خدمه مسافری | متصدیان رختکن، امانات و اتاق پرو | مهمانداران و متصدیان خدمات مسافران | رؤسای قطار و مدیران محوطه راه‌آهن | متصدیان فروش بلیت، رزرواسیون و خدمات سفر | نگهبانان و ماموران حراست | رانندگان خودروهای سرویس و تشریفات | رانندگان مترو و تراموا | ماموران بازرسی و کنترل امنیتی حمل‌ونقل | راهنماها، متصدیان سالن و بلیط‌گیرها</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -560,22 +560,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>نرم‌افزار دیسپچ و اعزام رایانه‌ای | نرم‌افزار نقشه‌خوانی و مسیریابی | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Word</t>
+          <t>نرم‌افزار اعزام به کمک کامپیوتر | نرم‌افزار نقشه‌برداری | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Word</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال | درک مطلب | سخن گفتن | یادگیری فعال | نظارت</t>
+          <t>تفکر انتقادی | گوش دادن فعال | درک مطلب | سخن گفتن | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | ایمنی و امنیت عمومی | مدیریت و امور اداری | امور حقوقی و دولتی | ترابری | آموزش و تدریس | پزشکی و دندانپزشکی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | ایمنی و امنیت عمومی | مدیریت و اداره | قانون و دولت | حمل و نقل | آموزش و پرورش | پزشکی و دندان‌پزشکی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | حساسیت به مسئله | بیان شفاهی | استدلال قیاسی | دید نزدیک | تشخیص گفتار | وضوح گفتار | دید دور | قدرت ایستا | زمان واکنش | جهت‌یابی پاسخ | هماهنگی چندعضوی | ثبات دست و بازو | تقسیم توجه | جهت‌یابی فضایی | مرتب‌سازی اطلاعات | استدلال استقرایی | درک کتبی | چابکی دستی | توجه انتخابی | سرعت ادراک | انعطاف‌پذیری در جمع‌بندی | انعطاف‌پذیری طبقه‌بندی | درک عمق | قدرت عضلات تنه | دقت کنترل</t>
+          <t>درک شفاهی | حساسیت به مسئله | بیان شفاهی | استدلال قیاسی | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | بینایی دور | قدرت ایستا | زمان عکس‌العمل | جهت‌گیری پاسخ | هماهنگی چند عضو | ثبات دست و بازو | تقسیم توجه | جهت‌گیری فضایی | ترتیب‌دهی اطلاعات | استدلال استقرایی | درک کتبی | مهارت دستی | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | درک عمق | قدرت تنه | دقت کنترل</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>پرستاران بخش مراقبت‌های ویژه | دستیاران متخصص بیهوشی | دیسپچرها (به‌جز پلیس، آتش‌نشانی و آمبولانس) | مدیران مدیریت بحران و فوریت‌ها | تکنسین‌های فوریت‌های پزشکی | پزشکان طب اورژانس | مراقبان سلامت در منزل | بهیاران و کمک‌پرستاران دارای مجوز | نجات‌غریق‌ها و سایر مشاغل امداد و نجات تفریحی | دستیاران پزشکی | مدیران خدمات درمانی و بهداشتی | کمک‌بهیاران | نیروهای خدمات بیمارستان (برانکاردچی) | فوریت‌های پزشکی (تکنسین‌های پیش‌بیمارستانی) | مراقبان خدمات فردی | دستیاران فیزیوتراپی | اپراتورهای فوریت‌های پلیس و مراکز امدادی | پرستاران رسمی | دستیاران جراحی | تکنسین‌های اتاق عمل</t>
+          <t>پرستاران مراقبت‌های حاد | دستیاران متخصص بیهوشی | متصدیان دیسپاچ و اعزام | مدیران مدیریت بحران و پدافند غیرعامل | تکنسین‌های فوریت‌های پزشکی | پزشکان طب اورژانس | مراقبان سلامت و بهیاران مراقبت در منزل | بهیاران و کمک‌پرستاران دارای مجوز | ناجیان غریق، گشت اسکی و سایر مشاغل خدمات حفاظتی و امدادی تفریحی | کمک‌پزشکان و دستیاران مطب | مدیران خدمات درمانی و بهداشتی | کمک‌پرستاران | خدمات‌دهندگان و انتقال‌دهندگان بیمار | امدادگران و تکنسین‌های اورژانس (پارامدیک‌ها) | مراقبان خدمات شخصی و همراهان توان‌خواهان | کمک‌یاران فیزیوتراپی | اپراتورهای فوریت‌های پلیسی و امدادی | پرستاران | دستیاران جراحی | تکنسین‌های اتاق عمل</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | تفکر انتقادی | درک مطلب</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | درک مطلب</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | صنایع غذایی و تولید غذا | زبان انگلیسی | ترابری | ایمنی و امنیت عمومی | مدیریت و امور اداری</t>
+          <t>خدمات مشتری و شخصی | تولید مواد غذایی | زبان انگلیسی | حمل و نقل | ایمنی و امنیت عمومی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | دید نزدیک | وضوح گفتار | تشخیص گفتار | حساسیت به مسئله | استدلال قیاسی | درک کتبی | دید دور | قدرت عضلات تنه | قدرت ایستا | دقت کنترل | چابکی انگشتان | ثبات دست و بازو | انعطاف‌پذیری طبقه‌بندی | مرتب‌سازی اطلاعات | استدلال استقرایی</t>
+          <t>درک شفاهی | بیان شفاهی | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | حساسیت به مسئله | استدلال قیاسی | درک کتبی | بینایی دور | قدرت تنه | قدرت ایستا | دقت کنترل | مهارت انگشتان | ثبات دست و بازو | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>کارشناسان خرید محصولات کشاورزی | متصدیان باربری و حمل‌ونقل کالا | صندوق‌داران | متصدیان پیشخوان و کرایه کالا | ماموران ارسال کالا و پیک‌ها | کارشناسان خدمات پس از فروش و پشتیبانی مشتریان | دیسپچرها (به‌جز پلیس، آتش‌نشانی و آمبولانس) | فروشندگان دوره‌گرد، دستفروشان و روزنامه‌فروشان خیابانی | کارکنان فست‌فود و سفارش‌گیرندگان پیشخوان | رانندگان خودروهای سنگین، تریلی و کشنده | کارگران جابه‌جایی دستی بار و اثاثیه | رانندگان وانت و خودروهای باربری سبک | کارمندان ثبت و پیگیری سفارش‌ها | متصدیان پارکینگ | کارمندان باجه‌های پستی | نامه‌رسان‌ها و موزعین پست | فروشندگان خرده‌فروشی | کارشناسان فروش خدمات (به‌جز تبلیغات، بیمه، مالی و گردشگری) | کارمندان انبار، ورود و خروج کالا | چیدمان‌کنندگان کالا و متصدیان جمع‌آوری سفارش در انبار</t>
+          <t>خریداران و کارشناسان خرید محصولات کشاورزی | کارگزاران حمل‌ونقل و بار | صندوق‌داران | متصدیان باجه و کرایه کالا و خدمات | پیک‌ها و نامه‌رسان‌ها | کارشناسان خدمات و پشتیبانی مشتریان | متصدیان دیسپاچ و اعزام | بازاریابان حضوری و فروشندگان خیابانی | کارگران پیشخوان و فست‌فود | رانندگان خودروهای سنگین و کشنده‌ها | کارگران جابه‌جایی دستی بار، کالا و مصالح | رانندگان خودروهای باربری سبک و وانت‌بارها | متصدیان ثبت و پیگیری سفارش‌ها | متصدیان پارکینگ | متصدیان باجه و امور پستی | نامه‌رسان‌ها و موزعین پست | فروشندگان خرده‌فروشی | کارشناسان فروش خدمات (به‌جز تبلیغات، بیمه، خدمات مالی و گردشگری) | کارمندان انبار، ارسال و دریافت کالا | متصدیان چیدمان و آماده‌سازی سفارش</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -684,12 +684,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ترابری | ایمنی و امنیت عمومی | خدمات مشتریان و خدمات فردی | زبان انگلیسی | امور حقوقی و دولتی</t>
+          <t>حمل و نقل | ایمنی و امنیت عمومی | خدمات مشتری و شخصی | زبان انگلیسی | قانون و دولت</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>دید دور | جهت‌یابی فضایی | دقت کنترل | هماهنگی چندعضوی | جهت‌یابی پاسخ | کنترل سرعت | زمان واکنش | حساسیت به مسئله | دید نزدیک | درک عمق | توجه انتخابی | استدلال قیاسی | درک شفاهی | درک کتبی | حساسیت به شنوایی | حساسیت به درخشش | دید محیطی | دید در شب | قدرت ایستا | چابکی دستی | ثبات دست و بازو | تقسیم توجه | تجسم فضایی | انعطاف‌پذیری در جمع‌بندی | انعطاف‌پذیری طبقه‌بندی | مرتب‌سازی اطلاعات | بیان شفاهی | وضوح گفتار | تشخیص گفتار | توجه شنیداری</t>
+          <t>بینایی دور | جهت‌گیری فضایی | دقت کنترل | هماهنگی چند عضو | جهت‌گیری پاسخ | کنترل نرخ | زمان عکس‌العمل | حساسیت به مسئله | بینایی نزدیک | درک عمق | توجه انتخابی | استدلال قیاسی | درک شفاهی | درک کتبی | حساسیت شنوایی | حساسیت به درخشندگی شدید | بینایی محیطی | بینایی در شب | قدرت ایستا | مهارت دستی | ثبات دست و بازو | تقسیم توجه | تجسم | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | بیان شفاهی | وضوح گفتار | تشخیص گفتار | توجه شنیداری</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>رانندگان اتوبوس‌های درون‌شهری و برون‌شهری | مکانیک‌های خودروهای سنگین و متخصصان موتورهای دیزلی | اپراتورهای جرثقیل و بالابرهای برجی | دیسپچرها (به‌جز پلیس، آتش‌نشانی و آمبولانس) | کارگران نگهداری و راهداری جاده‌ها | اپراتورهای وینچ و بالابرهای صنعتی | رانندگان تراکتور و لیفتراک‌های صنعتی | کارگران جابه‌جایی دستی بار و اثاثیه | رانندگان وانت و خودروهای باربری سبک | اپراتورهای ماشین‌آلات بارگیری و انتقال در معادن زیرزمینی | لکوموتیورانان | اپراتورهای ماشین‌آلات سنگین راه‌سازی و ساختمانی | اپراتورهای دستگاه‌های شمع‌کوبی | راهبران محوطه راه‌آهن و اپراتورهای دیزل‌های مانوری | ماموران ترمز، سوزن‌بانان و علائم راه‌آهن و آتشکاران لکوموتیو | رئیسان قطار و مسئولان محوطه راه‌آهن | ماموران جمع‌آوری زباله و مواد بازیافتی | رانندگان خودروهای سرویس و رانندگان اختصاصی | متصدیان بارگیری مخازن، تانکرها و کشتی‌ها | رانندگان تاکسی</t>
+          <t>رانندگان اتوبوس‌های درون‌شهری و برون‌شهری | مکانیک اتوبوس و کامیون و متخصص موتورهای دیزلی | اپراتورهای جرثقیل و تاورکرین | متصدیان دیسپاچ و اعزام | کارگران راهداری و نگهداری جاده‌ها | اپراتورهای بالابر و وینچ | رانندگان و اپراتورهای تراکتور و لیفتراک صنعتی | کارگران جابه‌جایی دستی بار، کالا و مصالح | رانندگان خودروهای باربری سبک و وانت‌بارها | اپراتورهای ماشین‌های بارگیری و حمل در معادن زیرزمینی | لکوموتیورانان | اپراتورهای ماشین‌آلات سنگین و تجهیزات عمرانی | اپراتورهای دستگاه شمع‌کوب | لکوموتیورانان محوطه راه‌آهن و رانندگان لکوموتیوهای کوچک مانوری | متصدیان ترمز، علائم و سوزن‌بانی راه‌آهن و آتشکاران لکوموتیو | رؤسای قطار و مدیران محوطه راه‌آهن | متصدیان و رانندگان جمع‌آوری پسماند و مواد بازیافتی | رانندگان خودروهای سرویس و تشریفات | متصدیان بارگیری مخزن‌دار ریلی، تانکر جاده‌ای و کشتی | رانندگان تاکسی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | نظارت | درک مطلب | تفکر انتقادی</t>
+          <t>گوش دادن فعال | سخن گفتن | نظارت | درک مطلب | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | ترابری | خدمات مشتریان و خدمات فردی</t>
+          <t>زبان انگلیسی | حمل و نقل | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>هماهنگی چندعضوی | دید دور | جهت‌یابی فضایی | حساسیت به مسئله | دید نزدیک | استقامت بدنی | قدرت عضلات تنه | قدرت ایستا | زمان واکنش | دقت کنترل | چابکی دستی | استدلال قیاسی | بیان شفاهی | درک شفاهی | درک کتبی | انعطاف‌پذیری کششی | جهت‌یابی پاسخ | سرعت ادراک | مرتب‌سازی اطلاعات | استدلال استقرایی | وضوح گفتار | تشخیص گفتار | درک عمق</t>
+          <t>هماهنگی چند عضو | بینایی دور | جهت‌گیری فضایی | حساسیت به مسئله | بینایی نزدیک | استقامت | قدرت تنه | قدرت ایستا | زمان عکس‌العمل | دقت کنترل | مهارت دستی | استدلال قیاسی | بیان شفاهی | درک شفاهی | درک کتبی | انعطاف‌پذیری دامنه حرکت | جهت‌گیری پاسخ | سرعت ادراکی | ترتیب‌دهی اطلاعات | استدلال استقرایی | وضوح گفتار | تشخیص گفتار | درک عمق</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>رانندگان اتوبوس‌های درون‌شهری و برون‌شهری | متصدیان باربری و حمل‌ونقل کالا | ماموران ارسال کالا و پیک‌ها | دیسپچرها (به‌جز پلیس، آتش‌نشانی و آمبولانس) | رانندگان توزیع و فروش مویرگی | سرپرستان رده اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابه‌جایی بار | رانندگان خودروهای سنگین و کشنده‌ها | رانندگان تراکتور و لیفتراک‌های صنعتی | متصدیان پارکینگ | کارمندان باجه‌های پستی | نامه‌رسان‌ها و موزعین پست | رئیسان قطار و مسئولان محوطه راه‌آهن | ماموران جمع‌آوری زباله و مواد بازیافتی | کارمندان انبار، ورود و خروج کالا | رانندگان خودروهای سرویس و رانندگان اختصاصی | چیدمان‌کنندگان کالا و متصدیان جمع‌آوری سفارش در انبار | متصدیان بارگیری مخازن، تانکرها و کشتی‌ها | رانندگان تاکسی | بازرسان حمل‌ونقل | بازرسان ناوگان، تجهیزات و سامانه‌های ترابری (به‌جز هوانوردی)</t>
+          <t>رانندگان اتوبوس‌های درون‌شهری و برون‌شهری | کارگزاران حمل‌ونقل و بار | پیک‌ها و نامه‌رسان‌ها | متصدیان دیسپاچ و اعزام | رانندگان توزیع و فروش مویرگی | سرپرستان رده‌اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابه‌جایی بار | رانندگان خودروهای سنگین و کشنده‌ها | رانندگان و اپراتورهای تراکتور و لیفتراک صنعتی | متصدیان پارکینگ | متصدیان باجه و امور پستی | نامه‌رسان‌ها و موزعین پست | رؤسای قطار و مدیران محوطه راه‌آهن | متصدیان و رانندگان جمع‌آوری پسماند و مواد بازیافتی | کارمندان انبار، ارسال و دریافت کالا | رانندگان خودروهای سرویس و تشریفات | متصدیان چیدمان و آماده‌سازی سفارش | متصدیان بارگیری مخزن‌دار ریلی، تانکر جاده‌ای و کشتی | رانندگان تاکسی | بازرسان ترابری و حمل‌ونقل | بازرسان سامانه‌ها، تجهیزات و وسایل نقلیه ترابری (به‌جز هوانوردی)</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -788,22 +788,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>نرم‌افزار AOL MapQuest | نرم‌افزار مرورگر وب | Microsoft Windows</t>
+          <t>نرم‌افزار AOL MapQuest | Microsoft Windows | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | نظارت | سخن گفتن | درک مطلب</t>
+          <t>گوش دادن فعال | تفکر انتقادی | نظارت | سخن گفتن | درک مطلب</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ترابری | ایمنی و امنیت عمومی | خدمات مشتریان و خدمات فردی | زبان انگلیسی | مکانیک | امور حقوقی و دولتی | جغرافیا</t>
+          <t>حمل و نقل | ایمنی و امنیت عمومی | خدمات مشتری و شخصی | زبان انگلیسی | مکانیک | قانون و دولت | جغرافیا</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>دید دور | دید نزدیک | زمان واکنش | حساسیت به مسئله | درک عمق | تشخیص گفتار | دید محیطی | هماهنگی چندعضوی | دقت کنترل | توجه شنیداری | درک شفاهی | جهت‌یابی فضایی | وضوح گفتار | تشخیص رنگ‌ها | کنترل سرعت | جهت‌یابی پاسخ | ثبات دست و بازو | تقسیم توجه | توجه انتخابی | مرتب‌سازی اطلاعات | بیان شفاهی | استدلال قیاسی</t>
+          <t>بینایی دور | بینایی نزدیک | زمان عکس‌العمل | حساسیت به مسئله | درک عمق | تشخیص گفتار | بینایی محیطی | هماهنگی چند عضو | دقت کنترل | توجه شنیداری | درک شفاهی | جهت‌گیری فضایی | وضوح گفتار | تشخیص رنگ بصری | کنترل نرخ | جهت‌گیری پاسخ | ثبات دست و بازو | تقسیم توجه | توجه انتخابی | ترتیب‌دهی اطلاعات | بیان شفاهی | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>کنترلرهای ترافیک هوایی | رانندگان و خدمه آمبولانس (به‌جز تکنسین‌های فوریت‌های پزشکی) | رانندگان اتوبوس‌های درون‌شهری و برون‌شهری | خلبانان تجاری | نگهبانان تقاطع و پرچم‌داران راهنمایی | دیسپچرها (به‌جز پلیس، آتش‌نشانی و آمبولانس) | تکنسین‌های فوریت‌های پزشکی | رانندگان خودروهای سنگین و کشنده‌ها | رانندگان وانت و خودروهای باربری سبک | لکوموتیورانان | کارشناسان اعمال قانون و کنترل پارک خودرو | خدمه و مهمانداران مسافری | راهبران محوطه راه‌آهن و اپراتورهای دیزل‌های مانوری | ماموران ترمز، سوزن‌بانان و علائم راه‌آهن و آتشکاران لکوموتیو | رئیسان قطار و مسئولان محوطه راه‌آهن | مراقبان سرویس مدارس | رانندگان خودروهای سرویس و رانندگان اختصاصی | راهبران مترو و تراموا | رانندگان تاکسی | پلیس ترانزیت و راه‌آهن</t>
+          <t>کنترلرهای ترافیک هوایی | رانندگان و خدمه آمبولانس، به‌جز تکنسین‌های فوریت‌های پزشکی | رانندگان اتوبوس‌های درون‌شهری و برون‌شهری | خلبانان تجاری | نگهبانان عبور و مرور و پرچم‌داران ترافیکی | متصدیان دیسپاچ و اعزام | تکنسین‌های فوریت‌های پزشکی | رانندگان خودروهای سنگین و کشنده‌ها | رانندگان خودروهای باربری سبک و وانت‌بارها | لکوموتیورانان | ماموران کنترل و اعمال قانون پارک دوبله و توقف | مهمانداران و متصدیان خدمات مسافران | لکوموتیورانان محوطه راه‌آهن و رانندگان لکوموتیوهای کوچک مانوری | متصدیان ترمز، علائم و سوزن‌بانی راه‌آهن و آتشکاران لکوموتیو | رؤسای قطار و مدیران محوطه راه‌آهن | مراقبین و متصدیان سرویس مدارس | رانندگان خودروهای سرویس و تشریفات | رانندگان مترو و تراموا | رانندگان تاکسی | پلیس ترانزیت و راه‌آهن</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -845,22 +845,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>نرم‌افزار AOL MapQuest | نرم‌افزار Microsoft MapPoint | نرم‌افزار مرورگر وب | Microsoft Windows</t>
+          <t>نرم‌افزار AOL MapQuest | نرم‌افزار Microsoft MapPoint | Microsoft Windows | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | سخن گفتن | نظارت</t>
+          <t>گوش دادن فعال | تفکر انتقادی | سخن گفتن | نظارت</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ترابری | خدمات مشتریان و خدمات فردی | ایمنی و امنیت عمومی | زبان انگلیسی | امور حقوقی و دولتی</t>
+          <t>حمل و نقل | خدمات مشتری و شخصی | ایمنی و امنیت عمومی | زبان انگلیسی | قانون و دولت</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>دید دور | دقت کنترل | هماهنگی چندعضوی | درک عمق | جهت‌یابی پاسخ | زمان واکنش | جهت‌یابی فضایی | دید نزدیک | کنترل سرعت | حساسیت به مسئله | توجه انتخابی | وضوح گفتار | درک شفاهی | بیان شفاهی | تقسیم توجه | دید محیطی | تشخیص گفتار | توجه شنیداری | ثبات دست و بازو | درک کتبی | حساسیت به درخشش | دید در شب | مرتب‌سازی اطلاعات | استدلال قیاسی</t>
+          <t>بینایی دور | دقت کنترل | هماهنگی چند عضو | درک عمق | جهت‌گیری پاسخ | زمان عکس‌العمل | جهت‌گیری فضایی | بینایی نزدیک | کنترل نرخ | حساسیت به مسئله | توجه انتخابی | وضوح گفتار | درک شفاهی | بیان شفاهی | تقسیم توجه | بینایی محیطی | تشخیص گفتار | توجه شنیداری | ثبات دست و بازو | درک کتبی | حساسیت به درخشندگی شدید | بینایی در شب | ترتیب‌دهی اطلاعات | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>کنترلرهای ترافیک هوایی | کارشناسان عملیات فرودگاهی | باربران فرودگاه و هتل | رانندگان سرویس مدارس | دیسپچرها (به‌جز پلیس، آتش‌نشانی و آمبولانس) | مهمانداران هواپیما | رانندگان خودروهای سنگین و کشنده‌ها | رانندگان وانت و خودروهای باربری سبک | لکوموتیورانان | متصدیان پارکینگ | خدمه و مهمانداران مسافری | راهبران محوطه راه‌آهن و اپراتورهای دیزل‌های مانوری | ماموران ترمز، سوزن‌بانان و علائم راه‌آهن و آتشکاران لکوموتیو | رئیسان قطار و مسئولان محوطه راه‌آهن | متصدیان رزرو، صدور بلیط و کارمندان آژانس‌های مسافرتی | مراقبان سرویس مدارس | رانندگان خودروهای سرویس و رانندگان اختصاصی | راهبران مترو و تراموا | رانندگان تاکسی | پلیس ترانزیت و راه‌آهن</t>
+          <t>کنترلرهای ترافیک هوایی | کارشناسان عملیات فرودگاهی | متصدیان حمل بار و خدمات هتل | رانندگان سرویس مدارس | متصدیان دیسپاچ و اعزام | مهمانداران هواپیما | رانندگان خودروهای سنگین و کشنده‌ها | رانندگان خودروهای باربری سبک و وانت‌بارها | لکوموتیورانان | متصدیان پارکینگ | مهمانداران و متصدیان خدمات مسافران | لکوموتیورانان محوطه راه‌آهن و رانندگان لکوموتیوهای کوچک مانوری | متصدیان ترمز، علائم و سوزن‌بانی راه‌آهن و آتشکاران لکوموتیو | رؤسای قطار و مدیران محوطه راه‌آهن | متصدیان فروش بلیت، رزرواسیون و خدمات سفر | مراقبین و متصدیان سرویس مدارس | رانندگان خودروهای سرویس و تشریفات | رانندگان مترو و تراموا | رانندگان تاکسی | پلیس ترانزیت و راه‌آهن</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>شنیدن فعال | نظارت | تفکر انتقادی | سخن گفتن</t>
+          <t>گوش دادن فعال | نظارت | تفکر انتقادی | سخن گفتن</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | ترابری | ایمنی و امنیت عمومی | زبان انگلیسی | پرسنلی و منابع انسانی | اداری | مدیریت و امور اداری | آموزش و تدریس | تولید و پردازش | امور حقوقی و دولتی | روان‌شناسی | اقتصاد و حسابداری | ارتباطات و رسانه‌ها | ریاضیات | فروش و بازاریابی</t>
+          <t>خدمات مشتری و شخصی | حمل و نقل | ایمنی و امنیت عمومی | زبان انگلیسی | پرسنل و منابع انسانی | اداری | مدیریت و اداره | آموزش و پرورش | تولید و فرآوری | قانون و دولت | روان‌شناسی | اقتصاد و حسابداری | ارتباطات و رسانه | ریاضیات | فروش و بازاریابی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>دید نزدیک | دید دور | هماهنگی چندعضوی | دقت کنترل | حساسیت به مسئله | درک شفاهی | درک عمق | وضوح گفتار | جهت‌یابی فضایی | توجه انتخابی | کنترل سرعت | زمان واکنش | تشخیص گفتار | دید محیطی | ثبات دست و بازو | تقسیم توجه | مرتب‌سازی اطلاعات | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | جهت‌یابی پاسخ | سرعت ادراک | توجه شنیداری | دید در شب</t>
+          <t>بینایی نزدیک | بینایی دور | هماهنگی چند عضو | دقت کنترل | حساسیت به مسئله | درک شفاهی | درک عمق | وضوح گفتار | جهت‌گیری فضایی | توجه انتخابی | کنترل نرخ | زمان عکس‌العمل | تشخیص گفتار | بینایی محیطی | ثبات دست و بازو | تقسیم توجه | ترتیب‌دهی اطلاعات | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | جهت‌گیری پاسخ | سرعت ادراکی | توجه شنیداری | بینایی در شب</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>باربران فرودگاه و هتل | رانندگان سرویس مدارس | رانندگان اتوبوس‌های درون‌شهری و برون‌شهری | مکانیک‌های خودروهای سنگین و متخصصان موتورهای دیزلی | ماموران ارسال کالا و پیک‌ها | دیسپچرها (به‌جز پلیس، آتش‌نشانی و آمبولانس) | رانندگان توزیع و فروش مویرگی | رانندگان خودروهای سنگین و کشنده‌ها | رانندگان تراکتور و لیفتراک‌های صنعتی | رانندگان وانت و خودروهای باربری سبک | اپراتورهای ماشین‌آلات بارگیری و انتقال در معادن زیرزمینی | لکوموتیورانان | متصدیان پارکینگ | خدمه و مهمانداران مسافری | تعمیرکاران واگن‌های راه‌آهن | رئیسان قطار و مسئولان محوطه راه‌آهن | متصدیان رزرو، صدور بلیط و کارمندان آژانس‌های مسافرتی | راهبران مترو و تراموا | رانندگان تاکسی | بازرسان ناوگان، تجهیزات و سامانه‌های ترابری (به‌جز هوانوردی)</t>
+          <t>متصدیان حمل بار و خدمات هتل | رانندگان سرویس مدارس | رانندگان اتوبوس‌های درون‌شهری و برون‌شهری | مکانیک اتوبوس و کامیون و متخصص موتورهای دیزلی | پیک‌ها و نامه‌رسان‌ها | متصدیان دیسپاچ و اعزام | رانندگان توزیع و فروش مویرگی | رانندگان خودروهای سنگین و کشنده‌ها | رانندگان و اپراتورهای تراکتور و لیفتراک صنعتی | رانندگان خودروهای باربری سبک و وانت‌بارها | اپراتورهای ماشین‌های بارگیری و حمل در معادن زیرزمینی | لکوموتیورانان | متصدیان پارکینگ | مهمانداران و متصدیان خدمات مسافران | تعمیرکار واگن قطار | رؤسای قطار و مدیران محوطه راه‌آهن | متصدیان فروش بلیت، رزرواسیون و خدمات سفر | رانندگان مترو و تراموا | رانندگان تاکسی | بازرسان سامانه‌ها، تجهیزات و وسایل نقلیه ترابری (به‌جز هوانوردی)</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ترابری | خدمات مشتریان و خدمات فردی | جغرافیا | زبان انگلیسی | ایمنی و امنیت عمومی | امور حقوقی و دولتی | ریاضیات</t>
+          <t>حمل و نقل | خدمات مشتری و شخصی | جغرافیا | زبان انگلیسی | ایمنی و امنیت عمومی | قانون و دولت | ریاضیات</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>چابکی دستی | چابکی انگشتان | ثبات دست و بازو | هماهنگی چندعضوی | دقت کنترل | قدرت ایستا | قدرت عضلات تنه | استقامت بدنی | دید نزدیک | دید دور | درک عمق | هماهنگی عمومی بدن | تعادل عمومی بدن | انعطاف‌پذیری کششی | زمان واکنش | حساسیت به مسئله | درک شفاهی | توجه انتخابی | بیان شفاهی | وضوح گفتار | جهت‌یابی فضایی | تقسیم توجه</t>
+          <t>مهارت دستی | مهارت انگشتان | ثبات دست و بازو | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | قدرت تنه | استقامت | بینایی نزدیک | بینایی دور | درک عمق | هماهنگی کلی بدن | تعادل کلی بدن | انعطاف‌پذیری دامنه حرکت | زمان عکس‌العمل | حساسیت به مسئله | درک شفاهی | توجه انتخابی | بیان شفاهی | وضوح گفتار | جهت‌گیری فضایی | تقسیم توجه</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>رانندگان سرویس مدارس | رانندگان اتوبوس‌های درون‌شهری و برون‌شهری | مکانیک‌های خودروهای سنگین و متخصصان موتورهای دیزلی | ماموران ارسال کالا و پیک‌ها | دیسپچرها (به‌جز پلیس، آتش‌نشانی و آمبولانس) | رانندگان توزیع و فروش مویرگی | رانندگان خودروهای سنگین و کشنده‌ها | رانندگان تراکتور و لیفتراک‌های صنعتی | رانندگان وانت و خودروهای باربری سبک | اپراتورهای ماشین‌آلات بارگیری و انتقال در معادن زیرزمینی | لکوموتیورانان | متصدیان پارکینگ | خدمه و مهمانداران مسافری | تعمیرکاران واگن‌های راه‌آهن | راهبران محوطه راه‌آهن و اپراتورهای دیزل‌های مانوری | ماموران ترمز، سوزن‌بانان و علائم راه‌آهن و آتشکاران لکوموتیو | رئیسان قطار و مسئولان محوطه راه‌آهن | رانندگان خودروهای سرویس و رانندگان اختصاصی | راهبران مترو و تراموا | بازرسان ناوگان، تجهیزات و سامانه‌های ترابری (به‌جز هوانوردی)</t>
+          <t>رانندگان سرویس مدارس | رانندگان اتوبوس‌های درون‌شهری و برون‌شهری | مکانیک اتوبوس و کامیون و متخصص موتورهای دیزلی | پیک‌ها و نامه‌رسان‌ها | متصدیان دیسپاچ و اعزام | رانندگان توزیع و فروش مویرگی | رانندگان خودروهای سنگین و کشنده‌ها | رانندگان و اپراتورهای تراکتور و لیفتراک صنعتی | رانندگان خودروهای باربری سبک و وانت‌بارها | اپراتورهای ماشین‌های بارگیری و حمل در معادن زیرزمینی | لکوموتیورانان | متصدیان پارکینگ | مهمانداران و متصدیان خدمات مسافران | تعمیرکار واگن قطار | لکوموتیورانان محوطه راه‌آهن و رانندگان لکوموتیوهای کوچک مانوری | متصدیان ترمز، علائم و سوزن‌بانی راه‌آهن و آتشکاران لکوموتیو | رؤسای قطار و مدیران محوطه راه‌آهن | رانندگان خودروهای سرویس و تشریفات | رانندگان مترو و تراموا | بازرسان سامانه‌ها، تجهیزات و وسایل نقلیه ترابری (به‌جز هوانوردی)</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ترابری | ایمنی و امنیت عمومی | خدمات مشتریان و خدمات فردی | زبان انگلیسی | جغرافیا | مکانیک | امور حقوقی و دولتی</t>
+          <t>حمل و نقل | ایمنی و امنیت عمومی | خدمات مشتری و شخصی | زبان انگلیسی | جغرافیا | مکانیک | قانون و دولت</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>چابکی دستی | چابکی انگشتان | ثبات دست و بازو | هماهنگی چندعضوی | دقت کنترل | قدرت ایستا | قدرت عضلات تنه | استقامت بدنی | دید نزدیک | دید دور | درک عمق | هماهنگی عمومی بدن | تعادل عمومی بدن | انعطاف‌پذیری کششی | زمان واکنش | حساسیت به مسئله | درک شفاهی | توجه انتخابی</t>
+          <t>مهارت دستی | مهارت انگشتان | ثبات دست و بازو | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | قدرت تنه | استقامت | بینایی نزدیک | بینایی دور | درک عمق | هماهنگی کلی بدن | تعادل کلی بدن | انعطاف‌پذیری دامنه حرکت | زمان عکس‌العمل | حساسیت به مسئله | درک شفاهی | توجه انتخابی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>رانندگان خودروهای سنگین و کشنده‌ها | رانندگان وانت و خودروهای باربری سبک | رانندگان توزیع و فروش مویرگی | رانندگان خودروهای سرویس و رانندگان اختصاصی | رانندگان تاکسی | رانندگان سرویس مدارس | رانندگان اتوبوس‌های درون‌شهری و برون‌شهری | رانندگان و خدمه آمبولانس (به‌جز تکنسین‌های فوریت‌های پزشکی) | رانندگان تراکتور و لیفتراک‌های صنعتی | متصدیان پارکینگ | متصدیان خدمات خودرویی و شناورها | کارگران جابه‌جایی دستی بار و اثاثیه | ماموران جمع‌آوری زباله و مواد بازیافتی | ماموران ارسال کالا و پیک‌ها | متصدیان باربری و حمل‌ونقل کالا | دیسپچرها (به‌جز پلیس، آتش‌نشانی و آمبولانس) | بازرسان حمل‌ونقل | سرپرستان رده اول سایر کارکنان ترابری | مدیران ترابری، انبارداری و توزیع | اپراتورهای جرثقیل و بالابرهای برجی</t>
+          <t>رانندگان خودروهای سنگین و کشنده‌ها | رانندگان خودروهای باربری سبک و وانت‌بارها | رانندگان توزیع و فروش مویرگی | رانندگان خودروهای سرویس و تشریفات | رانندگان تاکسی | رانندگان سرویس مدارس | رانندگان اتوبوس‌های درون‌شهری و برون‌شهری | رانندگان و خدمه آمبولانس، به‌جز تکنسین‌های فوریت‌های پزشکی | رانندگان و اپراتورهای تراکتور و لیفتراک صنعتی | متصدیان پارکینگ | متصدیان جایگاه‌های سوخت و خدمات وسایل نقلیه و شناورها | کارگران جابه‌جایی دستی بار، کالا و مصالح | متصدیان و رانندگان جمع‌آوری پسماند و مواد بازیافتی | پیک‌ها و نامه‌رسان‌ها | کارگزاران حمل‌ونقل و بار | متصدیان دیسپاچ و اعزام | بازرسان ترابری و حمل‌ونقل | سرپرستان رده‌اول سایر کارکنان ترابری و حمل‌ونقل | مدیران حمل‌ونقل، انبارداری و توزیع | اپراتورهای جرثقیل و تاورکرین</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
